--- a/data/trans_bre/IP25-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>-7,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-10,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 15,91</t>
+          <t>-5,7; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 4,75</t>
+          <t>-14,49; 5,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 2,56</t>
+          <t>-16,09; 3,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,83; 35,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 39,05</t>
+          <t>-21,9; 9,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 8,4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-25,57; 4,49</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-24,3; 5,55</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>-2,22%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,22%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,58</t>
+          <t>-0,47; 4,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,26</t>
+          <t>-4,32; -0,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,35</t>
+          <t>-1,4; 3,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,52; 4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,89</t>
+          <t>-4,35; -0,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -0,27</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 3,53</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-1,41; 3,48</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-1,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,96</t>
+          <t>-0,39; 6,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,69</t>
+          <t>-2,2; 2,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,68</t>
+          <t>-4,4; 0,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,4; 7,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 7,57</t>
+          <t>-2,22; 2,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,78</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 0,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,47; 0,78</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>2,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,83</t>
+          <t>-2,42; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,71</t>
+          <t>-2,69; 2,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,9</t>
+          <t>-0,19; 6,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,46; 3,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,01</t>
+          <t>-2,72; 2,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,82</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 6,37</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,18; 7,12</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>-2,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>-1,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,65</t>
+          <t>0,28; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,5</t>
+          <t>-4,65; 0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,09</t>
+          <t>-4,04; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,23; 6,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,52</t>
+          <t>-4,98; 0,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,39; 1,03</t>
         </is>
       </c>
     </row>
@@ -1108,12 +992,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
   </mergeCells>

--- a/data/trans_bre/IP25-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 14,55</t>
+          <t>-5,76; 15,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 5,22</t>
+          <t>-13,14; 5,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 3,23</t>
+          <t>-15,96; 4,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 35,23</t>
+          <t>-11,16; 39,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 9,77</t>
+          <t>-20,32; 9,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 5,55</t>
+          <t>-24,01; 7,94</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,49</t>
+          <t>-0,81; 4,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,31</t>
+          <t>-4,49; -0,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,33</t>
+          <t>-1,18; 3,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,76</t>
+          <t>-0,84; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; -0,35</t>
+          <t>-4,54; -0,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,48</t>
+          <t>-1,22; 3,77</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 6,96</t>
+          <t>-0,28; 6,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,73</t>
+          <t>-2,2; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,76</t>
+          <t>-4,44; 0,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,66</t>
+          <t>-0,25; 7,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,82</t>
+          <t>-2,22; 2,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,78</t>
+          <t>-4,47; 0,47</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,95</t>
+          <t>-2,37; 2,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,65</t>
+          <t>-2,81; 2,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,59</t>
+          <t>-0,45; 6,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,09</t>
+          <t>-2,42; 3,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,75</t>
+          <t>-2,85; 2,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,12</t>
+          <t>-0,46; 6,54</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,5</t>
+          <t>0,24; 5,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,54</t>
+          <t>-4,63; 0,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,93</t>
+          <t>-3,92; 1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,4</t>
+          <t>0,31; 6,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,6</t>
+          <t>-5,01; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,03</t>
+          <t>-4,27; 1,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 15,81</t>
+          <t>-5,99; 15,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 5,43</t>
+          <t>-14,23; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 4,67</t>
+          <t>-17,08; 2,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 39,01</t>
+          <t>-11,49; 39,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 9,19</t>
+          <t>-21,49; 8,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 7,94</t>
+          <t>-25,57; 4,49</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,49</t>
+          <t>-0,58; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,21</t>
+          <t>-4,48; -0,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,58</t>
+          <t>-1,74; 3,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,8</t>
+          <t>-0,6; 4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,24</t>
+          <t>-4,51; -0,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,77</t>
+          <t>-1,79; 3,53</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 6,46</t>
+          <t>-0,02; 6,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,83</t>
+          <t>-2,25; 2,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,47</t>
+          <t>-4,6; 0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,11</t>
+          <t>-0,02; 7,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,94</t>
+          <t>-2,27; 2,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,47</t>
+          <t>-4,64; 0,67</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,99</t>
+          <t>-2,26; 2,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,43</t>
+          <t>-2,74; 2,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 6,03</t>
+          <t>-0,32; 5,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,14</t>
+          <t>-2,32; 3,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,54</t>
+          <t>-2,77; 2,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,54</t>
+          <t>-0,33; 6,37</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,55</t>
+          <t>0,09; 5,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,41</t>
+          <t>-4,72; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,03</t>
+          <t>-3,84; 1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,48</t>
+          <t>0,1; 6,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,44</t>
+          <t>-5,12; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,15</t>
+          <t>-4,17; 1,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-10,54%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.970889758200315</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.388252474066334</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-6.581769291254014</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.1080860509211499</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07163868763094766</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1053922072269483</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,99; 15,91</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,23; 4,75</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-17,08; 2,56</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,49; 39,05</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-21,49; 8,4</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-25,57; 4,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.990355447844805</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-14.23186673435341</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-17.08115768820945</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.1148946545024491</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2149463823997203</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2556790356820838</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.91475105364373</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.74774910876451</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.557557870011315</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.3905030184645143</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.08401988695520249</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.04487661054917605</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,2</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-2,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 4,58</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,48; -0,26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 3,35</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,6; 4,89</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; -0,27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 3,53</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.795010168415756</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.200072922783392</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9304748783616312</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.0187857308932275</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.02223620257258846</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.009608121678747569</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,77%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.5790443846066541</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.483831961634658</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.740870932910306</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.005991531000162559</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.0451484708869854</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.01792336189554932</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,02; 6,96</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 2,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,6; 0,68</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,02; 7,57</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 2,78</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 0,67</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.578253671148032</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.2643583391418237</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.349177950296835</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.04889642138901563</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.002728645409198363</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03530132544610431</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.188279706108732</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.09521652084073517</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.751753646497789</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.0334985626284325</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0009703397848644584</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01773998197471297</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 2,83</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 2,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 5,9</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,32; 3,01</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,77; 2,82</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-0,33; 6,37</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.02069043824106784</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.25129235687128</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.60327186549568</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.0001939354409561912</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.02268138871794712</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.04636768635087974</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.960003549176368</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.689625383401702</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6759410318011586</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.07572296451829245</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.02779466957690313</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.006663172779967669</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3621529811062341</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01603994729747482</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.475565211435393</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.003737638312737996</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.0001644384238153797</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.0258695898442485</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.259552611149019</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.740411809012728</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.3166063068963464</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.02324745627662475</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02766758564803178</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.003279038983968778</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.826223484366415</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.712156510130321</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.896915008957093</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.03012259039928089</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02821278392117326</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.06372668977205861</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 5,65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,72; 0,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 1,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 6,52</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 0,55</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.776740117313381</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.173199715805918</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.493617665982028</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.03172082477166212</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02381458875773705</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01635533306248851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.08915016252287135</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.719499292334402</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.836271919237275</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.0009667227748420159</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05121490315252061</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04166839330405903</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.647938539766834</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4989331690560716</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.086920194524964</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.06523975511321876</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.005458926872619372</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.01207351016952813</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
